--- a/public/templates/transaction.xlsx
+++ b/public/templates/transaction.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="14145" windowHeight="8550"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="9" name="명세서" state="visible" r:id="rId4"/>
+    <sheet name="명세서" sheetId="9" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>거 래 일 자</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>)</t>
-  </si>
-  <si>
-    <t>부가세포함</t>
   </si>
   <si>
     <t>월</t>
@@ -139,130 +136,130 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="[DBNum4][$-412]General"/>
-    <numFmt numFmtId="165" formatCode="₩#,##0"/>
-    <numFmt numFmtId="166" formatCode="#,##0_);[Red](#,##0)"/>
-    <numFmt numFmtId="167" formatCode="0_ "/>
-    <numFmt numFmtId="168" formatCode="#,##0_ "/>
-    <numFmt numFmtId="169" formatCode="#,##0;[Red]#,##0"/>
-    <numFmt numFmtId="170" formatCode="&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="176" formatCode="[DBNum4][$-412]General"/>
+    <numFmt numFmtId="177" formatCode="\₩#,##0"/>
+    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="180" formatCode="#,##0_ "/>
+    <numFmt numFmtId="181" formatCode="#,##0;[Red]#,##0"/>
+    <numFmt numFmtId="182" formatCode="&quot;₩&quot;#,##0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="10"/>
       <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="22"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="12"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="10"/>
       <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="9"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="11"/>
       <name val="나눔고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
-      <scheme val="minor"/>
       <sz val="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="8"/>
       <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="11"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="11"/>
       <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1098,6 +1095,75 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1113,12 +1179,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1128,53 +1206,44 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1194,6 +1263,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1203,18 +1281,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1224,24 +1290,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1263,10 +1329,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1275,50 +1356,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1332,19 +1392,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1356,33 +1410,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1392,39 +1440,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1434,43 +1470,55 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1488,12 +1536,27 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1503,92 +1566,62 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1599,15 +1632,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1617,15 +1641,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1644,27 +1659,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1696,10 +1693,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
+        <xdr:cNvPr id="0" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1743,7 +1740,7 @@
         <xdr:cNvPr id="2" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2055,981 +2052,1058 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:BA26"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="2.33203125"/>
+  <sheetFormatPr defaultColWidth="2.375" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3.33203125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="3.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="2.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:31" ht="18" customHeight="1">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="7" t="s">
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="8"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="33"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="15"/>
+    <row r="2" spans="1:31" ht="18" customHeight="1">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
+      <c r="AB2" s="34"/>
+      <c r="AC2" s="34"/>
+      <c r="AD2" s="34"/>
+      <c r="AE2" s="35"/>
     </row>
-    <row r="3" ht="9.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:31" ht="9.9499999999999993" customHeight="1">
+      <c r="A3" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20" t="s">
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="16" t="s">
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="S3" s="18"/>
-      <c r="T3" s="19"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="8"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="33"/>
     </row>
-    <row r="4" ht="9.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="27"/>
+    <row r="4" spans="1:31" ht="9.9499999999999993" customHeight="1">
+      <c r="A4" s="50"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="47"/>
+      <c r="W4" s="47"/>
+      <c r="X4" s="47"/>
+      <c r="Y4" s="47"/>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="47"/>
+      <c r="AB4" s="47"/>
+      <c r="AC4" s="47"/>
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="48"/>
     </row>
-    <row r="5" ht="9.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="28" t="s">
+    <row r="5" spans="1:31" ht="9.9499999999999993" customHeight="1">
+      <c r="A5" s="50"/>
+      <c r="B5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="28" t="s">
+      <c r="C5" s="53"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="28" t="s">
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="30"/>
-      <c r="M5" s="31" t="s">
+      <c r="L5" s="54"/>
+      <c r="M5" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="28" t="s">
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="S5" s="29"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="34"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="28" t="s">
+      <c r="S5" s="53"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="63"/>
+      <c r="Z5" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="37"/>
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="52"/>
+      <c r="AC5" s="53"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="67"/>
     </row>
-    <row r="6" ht="9.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="42"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="43"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="23"/>
-      <c r="AE6" s="44"/>
+    <row r="6" spans="1:31" ht="9.9499999999999993" customHeight="1">
+      <c r="A6" s="50"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="60"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="66"/>
+      <c r="Z6" s="42"/>
+      <c r="AA6" s="44"/>
+      <c r="AB6" s="42"/>
+      <c r="AC6" s="43"/>
+      <c r="AD6" s="43"/>
+      <c r="AE6" s="68"/>
     </row>
-    <row r="7" ht="12.75" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="28" t="s">
+    <row r="7" spans="1:31" ht="12.75" customHeight="1">
+      <c r="A7" s="50"/>
+      <c r="B7" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="31" t="s">
+      <c r="C7" s="53"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="28" t="s">
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="57"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="29"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="32"/>
-      <c r="W7" s="32"/>
-      <c r="X7" s="32"/>
-      <c r="Y7" s="32"/>
-      <c r="Z7" s="32"/>
-      <c r="AA7" s="32"/>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="32"/>
-      <c r="AE7" s="33"/>
+      <c r="S7" s="53"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="55"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="56"/>
+      <c r="Z7" s="56"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="56"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="57"/>
     </row>
-    <row r="8" ht="12.75" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22" t="s">
+    <row r="8" spans="1:31" ht="12.75" customHeight="1">
+      <c r="A8" s="50"/>
+      <c r="B8" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="22" t="s">
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="59"/>
+      <c r="O8" s="59"/>
+      <c r="P8" s="60"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="S8" s="23"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="39"/>
-      <c r="W8" s="39"/>
-      <c r="X8" s="39"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="39"/>
-      <c r="AA8" s="39"/>
-      <c r="AB8" s="39"/>
-      <c r="AC8" s="39"/>
-      <c r="AD8" s="39"/>
-      <c r="AE8" s="40"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="58"/>
+      <c r="V8" s="59"/>
+      <c r="W8" s="59"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="59"/>
+      <c r="Z8" s="59"/>
+      <c r="AA8" s="59"/>
+      <c r="AB8" s="59"/>
+      <c r="AC8" s="59"/>
+      <c r="AD8" s="59"/>
+      <c r="AE8" s="60"/>
     </row>
-    <row r="9" ht="9.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="28" t="s">
+    <row r="9" spans="1:31" ht="9.9499999999999993" customHeight="1">
+      <c r="A9" s="50"/>
+      <c r="B9" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31" t="s">
+      <c r="C9" s="53"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="28" t="s">
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="31" t="s">
+      <c r="K9" s="54"/>
+      <c r="L9" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="28" t="s">
+      <c r="M9" s="56"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="57"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="S9" s="29"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="28" t="s">
+      <c r="S9" s="53"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="55"/>
+      <c r="V9" s="56"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="72"/>
+      <c r="Y9" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="33"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="56"/>
+      <c r="AC9" s="56"/>
+      <c r="AD9" s="56"/>
+      <c r="AE9" s="57"/>
     </row>
-    <row r="10" ht="9.95" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="50"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="52"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="49"/>
-      <c r="AA10" s="50"/>
-      <c r="AB10" s="51"/>
-      <c r="AC10" s="51"/>
-      <c r="AD10" s="51"/>
-      <c r="AE10" s="53"/>
+    <row r="10" spans="1:31" ht="9.9499999999999993" customHeight="1">
+      <c r="A10" s="51"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="74"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="69"/>
+      <c r="S10" s="70"/>
+      <c r="T10" s="71"/>
+      <c r="U10" s="73"/>
+      <c r="V10" s="74"/>
+      <c r="W10" s="74"/>
+      <c r="X10" s="75"/>
+      <c r="Y10" s="69"/>
+      <c r="Z10" s="71"/>
+      <c r="AA10" s="73"/>
+      <c r="AB10" s="74"/>
+      <c r="AC10" s="74"/>
+      <c r="AD10" s="74"/>
+      <c r="AE10" s="76"/>
     </row>
-    <row r="11" ht="9" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="54" t="s">
+    <row r="11" spans="1:31" ht="9" customHeight="1">
+      <c r="A11" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="61" t="s">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="84"/>
+      <c r="O11" s="84"/>
+      <c r="P11" s="87"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="S11" s="62"/>
-      <c r="T11" s="62"/>
-      <c r="U11" s="62"/>
-      <c r="V11" s="62"/>
-      <c r="W11" s="62"/>
-      <c r="X11" s="62"/>
-      <c r="Y11" s="62"/>
-      <c r="Z11" s="55" t="s">
+      <c r="S11" s="91"/>
+      <c r="T11" s="91"/>
+      <c r="U11" s="91"/>
+      <c r="V11" s="91"/>
+      <c r="W11" s="91"/>
+      <c r="X11" s="91"/>
+      <c r="Y11" s="91"/>
+      <c r="Z11" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="AA11" s="59" t="s">
+      <c r="AA11" s="87"/>
+      <c r="AB11" s="87"/>
+      <c r="AC11" s="87"/>
+      <c r="AD11" s="87"/>
+      <c r="AE11" s="93"/>
+    </row>
+    <row r="12" spans="1:31" ht="9" customHeight="1">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="86"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="86"/>
+      <c r="P12" s="89"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="92"/>
+      <c r="T12" s="92"/>
+      <c r="U12" s="92"/>
+      <c r="V12" s="92"/>
+      <c r="W12" s="92"/>
+      <c r="X12" s="92"/>
+      <c r="Y12" s="92"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="89"/>
+      <c r="AB12" s="89"/>
+      <c r="AC12" s="89"/>
+      <c r="AD12" s="89"/>
+      <c r="AE12" s="94"/>
+    </row>
+    <row r="13" spans="1:31" ht="17.45" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AB11" s="59"/>
-      <c r="AC11" s="59"/>
-      <c r="AD11" s="59"/>
-      <c r="AE11" s="63"/>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="97" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="97" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="98"/>
+      <c r="P13" s="99"/>
+      <c r="Q13" s="97" t="s">
+        <v>25</v>
+      </c>
+      <c r="R13" s="98"/>
+      <c r="S13" s="99"/>
+      <c r="T13" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="U13" s="98"/>
+      <c r="V13" s="98"/>
+      <c r="W13" s="99"/>
+      <c r="X13" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y13" s="98"/>
+      <c r="Z13" s="98"/>
+      <c r="AA13" s="98"/>
+      <c r="AB13" s="100"/>
+      <c r="AC13" s="101" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD13" s="102"/>
+      <c r="AE13" s="103"/>
     </row>
-    <row r="12" ht="9" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" s="64"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="68"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="70"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="72"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="72"/>
-      <c r="V12" s="72"/>
-      <c r="W12" s="72"/>
-      <c r="X12" s="72"/>
-      <c r="Y12" s="72"/>
-      <c r="Z12" s="65"/>
-      <c r="AA12" s="69"/>
-      <c r="AB12" s="69"/>
-      <c r="AC12" s="69"/>
-      <c r="AD12" s="69"/>
-      <c r="AE12" s="73"/>
+    <row r="14" spans="1:31" ht="17.45" customHeight="1">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="104"/>
+      <c r="O14" s="105"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="107"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="109"/>
+      <c r="T14" s="110"/>
+      <c r="U14" s="111"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="112"/>
+      <c r="X14" s="110"/>
+      <c r="Y14" s="111"/>
+      <c r="Z14" s="111"/>
+      <c r="AA14" s="111"/>
+      <c r="AB14" s="112"/>
+      <c r="AC14" s="110"/>
+      <c r="AD14" s="111"/>
+      <c r="AE14" s="113"/>
     </row>
-    <row r="13" ht="17.45" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="77"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="76" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" s="77"/>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="76" t="s">
-        <v>26</v>
-      </c>
-      <c r="R13" s="77"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="U13" s="77"/>
-      <c r="V13" s="77"/>
-      <c r="W13" s="78"/>
-      <c r="X13" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y13" s="77"/>
-      <c r="Z13" s="77"/>
-      <c r="AA13" s="77"/>
-      <c r="AB13" s="79"/>
-      <c r="AC13" s="80" t="s">
+    <row r="15" spans="1:31" ht="17.45" customHeight="1">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="115"/>
+      <c r="K15" s="115"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="116"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="115"/>
+      <c r="P15" s="116"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="118"/>
+      <c r="S15" s="119"/>
+      <c r="T15" s="120"/>
+      <c r="U15" s="121"/>
+      <c r="V15" s="121"/>
+      <c r="W15" s="122"/>
+      <c r="X15" s="120"/>
+      <c r="Y15" s="121"/>
+      <c r="Z15" s="121"/>
+      <c r="AA15" s="121"/>
+      <c r="AB15" s="122"/>
+      <c r="AC15" s="120"/>
+      <c r="AD15" s="121"/>
+      <c r="AE15" s="123"/>
+    </row>
+    <row r="16" spans="1:31" ht="17.45" customHeight="1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="115"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="116"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="116"/>
+      <c r="Q16" s="117"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="119"/>
+      <c r="T16" s="120"/>
+      <c r="U16" s="121"/>
+      <c r="V16" s="121"/>
+      <c r="W16" s="122"/>
+      <c r="X16" s="120"/>
+      <c r="Y16" s="121"/>
+      <c r="Z16" s="121"/>
+      <c r="AA16" s="121"/>
+      <c r="AB16" s="122"/>
+      <c r="AC16" s="120"/>
+      <c r="AD16" s="121"/>
+      <c r="AE16" s="123"/>
+    </row>
+    <row r="17" spans="1:53" ht="17.45" customHeight="1">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="115"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="115"/>
+      <c r="M17" s="116"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="115"/>
+      <c r="P17" s="116"/>
+      <c r="Q17" s="117"/>
+      <c r="R17" s="118"/>
+      <c r="S17" s="119"/>
+      <c r="T17" s="120"/>
+      <c r="U17" s="121"/>
+      <c r="V17" s="121"/>
+      <c r="W17" s="122"/>
+      <c r="X17" s="120"/>
+      <c r="Y17" s="121"/>
+      <c r="Z17" s="121"/>
+      <c r="AA17" s="121"/>
+      <c r="AB17" s="122"/>
+      <c r="AC17" s="120"/>
+      <c r="AD17" s="121"/>
+      <c r="AE17" s="123"/>
+    </row>
+    <row r="18" spans="1:53" ht="17.45" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="116"/>
+      <c r="N18" s="114"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="116"/>
+      <c r="Q18" s="117"/>
+      <c r="R18" s="118"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="120"/>
+      <c r="U18" s="121"/>
+      <c r="V18" s="121"/>
+      <c r="W18" s="122"/>
+      <c r="X18" s="120"/>
+      <c r="Y18" s="121"/>
+      <c r="Z18" s="121"/>
+      <c r="AA18" s="121"/>
+      <c r="AB18" s="122"/>
+      <c r="AC18" s="120"/>
+      <c r="AD18" s="121"/>
+      <c r="AE18" s="123"/>
+    </row>
+    <row r="19" spans="1:53" ht="17.45" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="115"/>
+      <c r="L19" s="115"/>
+      <c r="M19" s="116"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="116"/>
+      <c r="Q19" s="117"/>
+      <c r="R19" s="118"/>
+      <c r="S19" s="119"/>
+      <c r="T19" s="120"/>
+      <c r="U19" s="121"/>
+      <c r="V19" s="121"/>
+      <c r="W19" s="122"/>
+      <c r="X19" s="120"/>
+      <c r="Y19" s="121"/>
+      <c r="Z19" s="121"/>
+      <c r="AA19" s="121"/>
+      <c r="AB19" s="122"/>
+      <c r="AC19" s="120"/>
+      <c r="AD19" s="121"/>
+      <c r="AE19" s="123"/>
+    </row>
+    <row r="20" spans="1:53" ht="17.45" customHeight="1">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="125"/>
+      <c r="L20" s="125"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="124"/>
+      <c r="O20" s="125"/>
+      <c r="P20" s="126"/>
+      <c r="Q20" s="127"/>
+      <c r="R20" s="128"/>
+      <c r="S20" s="129"/>
+      <c r="T20" s="130"/>
+      <c r="U20" s="131"/>
+      <c r="V20" s="131"/>
+      <c r="W20" s="132"/>
+      <c r="X20" s="130"/>
+      <c r="Y20" s="131"/>
+      <c r="Z20" s="131"/>
+      <c r="AA20" s="131"/>
+      <c r="AB20" s="132"/>
+      <c r="AC20" s="130"/>
+      <c r="AD20" s="131"/>
+      <c r="AE20" s="133"/>
+      <c r="BA20" s="12"/>
+    </row>
+    <row r="21" spans="1:53" ht="16.5" customHeight="1">
+      <c r="A21" s="134" t="s">
         <v>29</v>
       </c>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="82"/>
-    </row>
-    <row r="14" ht="17.45" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="83"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="86"/>
-      <c r="G14" s="86"/>
-      <c r="H14" s="86"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
-      <c r="L14" s="86"/>
-      <c r="M14" s="87"/>
-      <c r="N14" s="85"/>
-      <c r="O14" s="86"/>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="88"/>
-      <c r="R14" s="89"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="91"/>
-      <c r="U14" s="92"/>
-      <c r="V14" s="92"/>
-      <c r="W14" s="93"/>
-      <c r="X14" s="91"/>
-      <c r="Y14" s="92"/>
-      <c r="Z14" s="92"/>
-      <c r="AA14" s="92"/>
-      <c r="AB14" s="93"/>
-      <c r="AC14" s="91"/>
-      <c r="AD14" s="92"/>
-      <c r="AE14" s="94"/>
-    </row>
-    <row r="15" ht="17.45" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" s="95"/>
-      <c r="B15" s="96"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="98"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="99"/>
-      <c r="N15" s="97"/>
-      <c r="O15" s="98"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="100"/>
-      <c r="R15" s="101"/>
-      <c r="S15" s="102"/>
-      <c r="T15" s="103"/>
-      <c r="U15" s="104"/>
-      <c r="V15" s="104"/>
-      <c r="W15" s="105"/>
-      <c r="X15" s="103"/>
-      <c r="Y15" s="104"/>
-      <c r="Z15" s="104"/>
-      <c r="AA15" s="104"/>
-      <c r="AB15" s="105"/>
-      <c r="AC15" s="103"/>
-      <c r="AD15" s="104"/>
-      <c r="AE15" s="106"/>
-    </row>
-    <row r="16" ht="17.45" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" s="95"/>
-      <c r="B16" s="96"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="99"/>
-      <c r="N16" s="97"/>
-      <c r="O16" s="98"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="100"/>
-      <c r="R16" s="101"/>
-      <c r="S16" s="102"/>
-      <c r="T16" s="103"/>
-      <c r="U16" s="104"/>
-      <c r="V16" s="104"/>
-      <c r="W16" s="105"/>
-      <c r="X16" s="103"/>
-      <c r="Y16" s="104"/>
-      <c r="Z16" s="104"/>
-      <c r="AA16" s="104"/>
-      <c r="AB16" s="105"/>
-      <c r="AC16" s="103"/>
-      <c r="AD16" s="104"/>
-      <c r="AE16" s="106"/>
-    </row>
-    <row r="17" ht="17.45" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17" s="95"/>
-      <c r="B17" s="96"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="97"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="100"/>
-      <c r="R17" s="101"/>
-      <c r="S17" s="102"/>
-      <c r="T17" s="103"/>
-      <c r="U17" s="104"/>
-      <c r="V17" s="104"/>
-      <c r="W17" s="105"/>
-      <c r="X17" s="103"/>
-      <c r="Y17" s="104"/>
-      <c r="Z17" s="104"/>
-      <c r="AA17" s="104"/>
-      <c r="AB17" s="105"/>
-      <c r="AC17" s="103"/>
-      <c r="AD17" s="104"/>
-      <c r="AE17" s="106"/>
-    </row>
-    <row r="18" ht="17.45" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A18" s="107"/>
-      <c r="B18" s="108"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="99"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="98"/>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="100"/>
-      <c r="R18" s="101"/>
-      <c r="S18" s="102"/>
-      <c r="T18" s="103"/>
-      <c r="U18" s="104"/>
-      <c r="V18" s="104"/>
-      <c r="W18" s="105"/>
-      <c r="X18" s="103"/>
-      <c r="Y18" s="104"/>
-      <c r="Z18" s="104"/>
-      <c r="AA18" s="104"/>
-      <c r="AB18" s="105"/>
-      <c r="AC18" s="103"/>
-      <c r="AD18" s="104"/>
-      <c r="AE18" s="106"/>
-    </row>
-    <row r="19" ht="17.45" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A19" s="107"/>
-      <c r="B19" s="108"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="99"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="98"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="100"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="102"/>
-      <c r="T19" s="103"/>
-      <c r="U19" s="104"/>
-      <c r="V19" s="104"/>
-      <c r="W19" s="105"/>
-      <c r="X19" s="103"/>
-      <c r="Y19" s="104"/>
-      <c r="Z19" s="104"/>
-      <c r="AA19" s="104"/>
-      <c r="AB19" s="105"/>
-      <c r="AC19" s="103"/>
-      <c r="AD19" s="104"/>
-      <c r="AE19" s="106"/>
-    </row>
-    <row r="20" ht="17.45" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A20" s="109"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="113"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="115"/>
-      <c r="S20" s="116"/>
-      <c r="T20" s="117"/>
-      <c r="U20" s="118"/>
-      <c r="V20" s="118"/>
-      <c r="W20" s="119"/>
-      <c r="X20" s="117"/>
-      <c r="Y20" s="118"/>
-      <c r="Z20" s="118"/>
-      <c r="AA20" s="118"/>
-      <c r="AB20" s="119"/>
-      <c r="AC20" s="117"/>
-      <c r="AD20" s="118"/>
-      <c r="AE20" s="120"/>
-      <c r="BA20" s="121"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21" s="122" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="123"/>
-      <c r="C21" s="124">
+      <c r="B21" s="135"/>
+      <c r="C21" s="138">
         <f>SUM(Q14:S20)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="125"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="127" t="s">
+      <c r="D21" s="139"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="144" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="145"/>
+      <c r="H21" s="146"/>
+      <c r="I21" s="147"/>
+      <c r="J21" s="147"/>
+      <c r="K21" s="148"/>
+      <c r="L21" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="128"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="130"/>
-      <c r="J21" s="130"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="132" t="s">
+      <c r="M21" s="153"/>
+      <c r="N21" s="156"/>
+      <c r="O21" s="157"/>
+      <c r="P21" s="158"/>
+      <c r="Q21" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="M21" s="133"/>
-      <c r="N21" s="134"/>
-      <c r="O21" s="135"/>
-      <c r="P21" s="136"/>
-      <c r="Q21" s="132" t="s">
+      <c r="R21" s="162"/>
+      <c r="S21" s="135"/>
+      <c r="T21" s="163"/>
+      <c r="U21" s="164"/>
+      <c r="V21" s="164"/>
+      <c r="W21" s="164"/>
+      <c r="X21" s="164"/>
+      <c r="Y21" s="165"/>
+      <c r="Z21" s="169" t="s">
         <v>33</v>
       </c>
-      <c r="R21" s="137"/>
-      <c r="S21" s="123"/>
-      <c r="T21" s="138"/>
-      <c r="U21" s="139"/>
-      <c r="V21" s="139"/>
-      <c r="W21" s="139"/>
-      <c r="X21" s="139"/>
-      <c r="Y21" s="140"/>
-      <c r="Z21" s="141" t="s">
+      <c r="AA21" s="170"/>
+      <c r="AB21" s="171"/>
+      <c r="AC21" s="169"/>
+      <c r="AD21" s="170"/>
+      <c r="AE21" s="175"/>
+    </row>
+    <row r="22" spans="1:53" ht="15" customHeight="1">
+      <c r="A22" s="136"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="142"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="AA21" s="142"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="141"/>
-      <c r="AD21" s="142"/>
-      <c r="AE21" s="144"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="149"/>
+      <c r="I22" s="150"/>
+      <c r="J22" s="150"/>
+      <c r="K22" s="151"/>
+      <c r="L22" s="154"/>
+      <c r="M22" s="155"/>
+      <c r="N22" s="159"/>
+      <c r="O22" s="160"/>
+      <c r="P22" s="161"/>
+      <c r="Q22" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" s="177"/>
+      <c r="S22" s="137"/>
+      <c r="T22" s="166"/>
+      <c r="U22" s="167"/>
+      <c r="V22" s="167"/>
+      <c r="W22" s="167"/>
+      <c r="X22" s="167"/>
+      <c r="Y22" s="168"/>
+      <c r="Z22" s="172"/>
+      <c r="AA22" s="173"/>
+      <c r="AB22" s="174"/>
+      <c r="AC22" s="172"/>
+      <c r="AD22" s="173"/>
+      <c r="AE22" s="176"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22" s="145"/>
-      <c r="B22" s="146"/>
-      <c r="C22" s="147"/>
-      <c r="D22" s="148"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="150" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="146"/>
-      <c r="H22" s="151"/>
-      <c r="I22" s="152"/>
-      <c r="J22" s="152"/>
-      <c r="K22" s="153"/>
-      <c r="L22" s="150"/>
-      <c r="M22" s="154"/>
-      <c r="N22" s="155"/>
-      <c r="O22" s="156"/>
-      <c r="P22" s="157"/>
-      <c r="Q22" s="150" t="s">
+    <row r="23" spans="1:53" ht="17.25" customHeight="1">
+      <c r="A23" s="178" t="s">
         <v>36</v>
       </c>
-      <c r="R22" s="158"/>
-      <c r="S22" s="146"/>
-      <c r="T22" s="159"/>
-      <c r="U22" s="160"/>
-      <c r="V22" s="160"/>
-      <c r="W22" s="160"/>
-      <c r="X22" s="160"/>
-      <c r="Y22" s="161"/>
-      <c r="Z22" s="162"/>
-      <c r="AA22" s="163"/>
-      <c r="AB22" s="164"/>
-      <c r="AC22" s="162"/>
-      <c r="AD22" s="163"/>
-      <c r="AE22" s="165"/>
+      <c r="B23" s="179"/>
+      <c r="C23" s="179"/>
+      <c r="D23" s="179"/>
+      <c r="E23" s="179"/>
+      <c r="F23" s="179"/>
+      <c r="G23" s="179"/>
+      <c r="H23" s="179"/>
+      <c r="I23" s="179"/>
+      <c r="J23" s="179"/>
+      <c r="K23" s="179"/>
+      <c r="L23" s="179"/>
+      <c r="M23" s="179"/>
+      <c r="N23" s="179"/>
+      <c r="O23" s="179"/>
+      <c r="P23" s="179"/>
+      <c r="Q23" s="179"/>
+      <c r="R23" s="179"/>
+      <c r="S23" s="179"/>
+      <c r="T23" s="179"/>
+      <c r="U23" s="179"/>
+      <c r="V23" s="179"/>
+      <c r="W23" s="179"/>
+      <c r="X23" s="179"/>
+      <c r="Y23" s="180"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="14"/>
+      <c r="AG23" s="15"/>
     </row>
-    <row r="23" ht="17.25" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="166" t="s">
+    <row r="24" spans="1:53" ht="15" customHeight="1">
+      <c r="A24" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="167"/>
-      <c r="C23" s="167"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="167"/>
-      <c r="F23" s="167"/>
-      <c r="G23" s="167"/>
-      <c r="H23" s="167"/>
-      <c r="I23" s="167"/>
-      <c r="J23" s="167"/>
-      <c r="K23" s="167"/>
-      <c r="L23" s="167"/>
-      <c r="M23" s="167"/>
-      <c r="N23" s="167"/>
-      <c r="O23" s="167"/>
-      <c r="P23" s="167"/>
-      <c r="Q23" s="167"/>
-      <c r="R23" s="167"/>
-      <c r="S23" s="167"/>
-      <c r="T23" s="167"/>
-      <c r="U23" s="167"/>
-      <c r="V23" s="167"/>
-      <c r="W23" s="167"/>
-      <c r="X23" s="167"/>
-      <c r="Y23" s="168"/>
-      <c r="Z23" s="169"/>
-      <c r="AA23" s="169"/>
-      <c r="AB23" s="169"/>
-      <c r="AC23" s="169"/>
-      <c r="AD23" s="169"/>
-      <c r="AE23" s="170"/>
-      <c r="AG23" s="171"/>
+      <c r="B24" s="182"/>
+      <c r="C24" s="182"/>
+      <c r="D24" s="182"/>
+      <c r="E24" s="182"/>
+      <c r="F24" s="182"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="182"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="182"/>
+      <c r="N24" s="182"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="182"/>
+      <c r="Q24" s="182"/>
+      <c r="R24" s="182"/>
+      <c r="S24" s="182"/>
+      <c r="T24" s="182"/>
+      <c r="U24" s="182"/>
+      <c r="V24" s="182"/>
+      <c r="W24" s="182"/>
+      <c r="X24" s="182"/>
+      <c r="Y24" s="183"/>
+      <c r="Z24" s="16"/>
+      <c r="AA24" s="16"/>
+      <c r="AB24" s="16"/>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="17"/>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="15"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="172" t="s">
+    <row r="25" spans="1:53" ht="15" customHeight="1">
+      <c r="A25" s="184"/>
+      <c r="B25" s="185"/>
+      <c r="C25" s="185"/>
+      <c r="D25" s="185"/>
+      <c r="E25" s="185"/>
+      <c r="F25" s="185"/>
+      <c r="G25" s="185"/>
+      <c r="H25" s="185"/>
+      <c r="I25" s="185"/>
+      <c r="J25" s="185"/>
+      <c r="K25" s="185"/>
+      <c r="L25" s="185"/>
+      <c r="M25" s="185"/>
+      <c r="N25" s="185"/>
+      <c r="O25" s="185"/>
+      <c r="P25" s="185"/>
+      <c r="Q25" s="185"/>
+      <c r="R25" s="185"/>
+      <c r="S25" s="185"/>
+      <c r="T25" s="185"/>
+      <c r="U25" s="185"/>
+      <c r="V25" s="185"/>
+      <c r="W25" s="185"/>
+      <c r="X25" s="185"/>
+      <c r="Y25" s="186"/>
+      <c r="Z25" s="187" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="173"/>
-      <c r="C24" s="173"/>
-      <c r="D24" s="173"/>
-      <c r="E24" s="173"/>
-      <c r="F24" s="173"/>
-      <c r="G24" s="173"/>
-      <c r="H24" s="173"/>
-      <c r="I24" s="173"/>
-      <c r="J24" s="173"/>
-      <c r="K24" s="173"/>
-      <c r="L24" s="173"/>
-      <c r="M24" s="173"/>
-      <c r="N24" s="173"/>
-      <c r="O24" s="173"/>
-      <c r="P24" s="173"/>
-      <c r="Q24" s="173"/>
-      <c r="R24" s="173"/>
-      <c r="S24" s="173"/>
-      <c r="T24" s="173"/>
-      <c r="U24" s="173"/>
-      <c r="V24" s="173"/>
-      <c r="W24" s="173"/>
-      <c r="X24" s="173"/>
-      <c r="Y24" s="174"/>
-      <c r="Z24" s="175"/>
-      <c r="AA24" s="175"/>
-      <c r="AB24" s="175"/>
-      <c r="AC24" s="175"/>
-      <c r="AD24" s="175"/>
-      <c r="AE24" s="176"/>
-      <c r="AF24" s="177"/>
-      <c r="AG24" s="171"/>
+      <c r="AA25" s="188"/>
+      <c r="AB25" s="188"/>
+      <c r="AC25" s="188"/>
+      <c r="AD25" s="188"/>
+      <c r="AE25" s="189"/>
+      <c r="AF25" s="19"/>
+      <c r="AG25" s="20"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="178"/>
-      <c r="B25" s="179"/>
-      <c r="C25" s="179"/>
-      <c r="D25" s="179"/>
-      <c r="E25" s="179"/>
-      <c r="F25" s="179"/>
-      <c r="G25" s="179"/>
-      <c r="H25" s="179"/>
-      <c r="I25" s="179"/>
-      <c r="J25" s="179"/>
-      <c r="K25" s="179"/>
-      <c r="L25" s="179"/>
-      <c r="M25" s="179"/>
-      <c r="N25" s="179"/>
-      <c r="O25" s="179"/>
-      <c r="P25" s="179"/>
-      <c r="Q25" s="179"/>
-      <c r="R25" s="179"/>
-      <c r="S25" s="179"/>
-      <c r="T25" s="179"/>
-      <c r="U25" s="179"/>
-      <c r="V25" s="179"/>
-      <c r="W25" s="179"/>
-      <c r="X25" s="179"/>
-      <c r="Y25" s="180"/>
-      <c r="Z25" s="181" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA25" s="182"/>
-      <c r="AB25" s="182"/>
-      <c r="AC25" s="182"/>
-      <c r="AD25" s="182"/>
-      <c r="AE25" s="183"/>
-      <c r="AF25" s="184"/>
-      <c r="AG25" s="185"/>
-    </row>
-    <row r="26" ht="6" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A26" s="186"/>
-      <c r="B26" s="186"/>
-      <c r="C26" s="187"/>
-      <c r="D26" s="187"/>
-      <c r="E26" s="187"/>
-      <c r="F26" s="187"/>
-      <c r="G26" s="187"/>
-      <c r="H26" s="187"/>
-      <c r="I26" s="187"/>
-      <c r="J26" s="187"/>
-      <c r="K26" s="187"/>
-      <c r="L26" s="187"/>
-      <c r="M26" s="187"/>
-      <c r="N26" s="187"/>
-      <c r="O26" s="187"/>
-      <c r="P26" s="187"/>
-      <c r="Q26" s="187"/>
-      <c r="R26" s="187"/>
-      <c r="S26" s="187"/>
-      <c r="T26" s="187"/>
-      <c r="U26" s="187"/>
-      <c r="V26" s="188"/>
-      <c r="W26" s="188"/>
-      <c r="X26" s="188"/>
-      <c r="Y26" s="188"/>
-      <c r="Z26" s="188"/>
-      <c r="AA26" s="188"/>
-      <c r="AB26" s="188"/>
-      <c r="AC26" s="188"/>
-      <c r="AD26" s="188"/>
-      <c r="AE26" s="188"/>
-      <c r="AF26" s="189"/>
-      <c r="AG26" s="171"/>
+    <row r="26" spans="1:53" ht="6" customHeight="1">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="23"/>
+      <c r="X26" s="23"/>
+      <c r="Y26" s="23"/>
+      <c r="Z26" s="23"/>
+      <c r="AA26" s="23"/>
+      <c r="AB26" s="23"/>
+      <c r="AC26" s="23"/>
+      <c r="AD26" s="23"/>
+      <c r="AE26" s="23"/>
+      <c r="AF26" s="24"/>
+      <c r="AG26" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="102">
+    <mergeCell ref="AC21:AE22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="A23:Y23"/>
+    <mergeCell ref="A24:Y25"/>
+    <mergeCell ref="Z25:AE25"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:E22"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:K22"/>
+    <mergeCell ref="L21:M22"/>
+    <mergeCell ref="N21:P22"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="T21:Y22"/>
+    <mergeCell ref="Z21:AB22"/>
+    <mergeCell ref="C19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="X19:AB19"/>
+    <mergeCell ref="AC19:AE19"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="X20:AB20"/>
+    <mergeCell ref="AC20:AE20"/>
+    <mergeCell ref="C17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:AB17"/>
+    <mergeCell ref="AC17:AE17"/>
+    <mergeCell ref="C18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="X18:AB18"/>
+    <mergeCell ref="AC18:AE18"/>
+    <mergeCell ref="C15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="X15:AB15"/>
+    <mergeCell ref="AC15:AE15"/>
+    <mergeCell ref="C16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="X16:AB16"/>
+    <mergeCell ref="AC16:AE16"/>
+    <mergeCell ref="C13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="X13:AB13"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="C14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="X14:AB14"/>
+    <mergeCell ref="AC14:AE14"/>
+    <mergeCell ref="B9:D10"/>
+    <mergeCell ref="E9:I10"/>
+    <mergeCell ref="J9:K10"/>
+    <mergeCell ref="L9:P10"/>
+    <mergeCell ref="R9:T10"/>
+    <mergeCell ref="U9:X10"/>
+    <mergeCell ref="Y9:Z10"/>
+    <mergeCell ref="AA9:AE10"/>
+    <mergeCell ref="A11:E12"/>
+    <mergeCell ref="F11:O12"/>
+    <mergeCell ref="P11:Q12"/>
+    <mergeCell ref="S11:Y12"/>
+    <mergeCell ref="AA11:AE12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="Z11:Z12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:Y2"/>
     <mergeCell ref="Z1:AE2"/>
@@ -3054,90 +3128,13 @@
     <mergeCell ref="U7:AE8"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="B9:D10"/>
-    <mergeCell ref="E9:I10"/>
-    <mergeCell ref="J9:K10"/>
-    <mergeCell ref="L9:P10"/>
-    <mergeCell ref="R9:T10"/>
-    <mergeCell ref="U9:X10"/>
-    <mergeCell ref="Y9:Z10"/>
-    <mergeCell ref="AA9:AE10"/>
-    <mergeCell ref="A11:E12"/>
-    <mergeCell ref="F11:O12"/>
-    <mergeCell ref="P11:Q12"/>
-    <mergeCell ref="S11:Y12"/>
-    <mergeCell ref="AA11:AE12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="C13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="T13:W13"/>
-    <mergeCell ref="X13:AB13"/>
-    <mergeCell ref="AC13:AE13"/>
-    <mergeCell ref="C14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="X14:AB14"/>
-    <mergeCell ref="AC14:AE14"/>
-    <mergeCell ref="C15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="X15:AB15"/>
-    <mergeCell ref="AC15:AE15"/>
-    <mergeCell ref="C16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="X16:AB16"/>
-    <mergeCell ref="AC16:AE16"/>
-    <mergeCell ref="C17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:AB17"/>
-    <mergeCell ref="AC17:AE17"/>
-    <mergeCell ref="C18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="X18:AB18"/>
-    <mergeCell ref="AC18:AE18"/>
-    <mergeCell ref="C19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="X19:AB19"/>
-    <mergeCell ref="AC19:AE19"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="X20:AB20"/>
-    <mergeCell ref="AC20:AE20"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:E22"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:K22"/>
-    <mergeCell ref="L21:M22"/>
-    <mergeCell ref="N21:P22"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="T21:Y22"/>
-    <mergeCell ref="Z21:AB22"/>
-    <mergeCell ref="AC21:AE22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="A23:Y23"/>
-    <mergeCell ref="A24:Y25"/>
-    <mergeCell ref="Z25:AE25"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="Z25" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.4" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/public/templates/transaction.xlsx
+++ b/public/templates/transaction.xlsx
@@ -1164,6 +1164,369 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1245,24 +1608,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1296,368 +1641,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1693,10 +1693,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Picture 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1737,10 +1737,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2064,456 +2064,456 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="18" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="32" t="s">
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
+      <c r="V1" s="150"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
+      <c r="Y1" s="150"/>
+      <c r="Z1" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="33"/>
+      <c r="AA1" s="153"/>
+      <c r="AB1" s="153"/>
+      <c r="AC1" s="153"/>
+      <c r="AD1" s="153"/>
+      <c r="AE1" s="154"/>
     </row>
     <row r="2" spans="1:31" ht="18" customHeight="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="35"/>
+      <c r="A2" s="157"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="152"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="155"/>
+      <c r="AA2" s="155"/>
+      <c r="AB2" s="155"/>
+      <c r="AC2" s="155"/>
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="156"/>
     </row>
     <row r="3" spans="1:31" ht="9.9499999999999993" customHeight="1">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="45" t="s">
+      <c r="C3" s="161"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="166" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="49" t="s">
+      <c r="F3" s="153"/>
+      <c r="G3" s="153"/>
+      <c r="H3" s="153"/>
+      <c r="I3" s="153"/>
+      <c r="J3" s="153"/>
+      <c r="K3" s="153"/>
+      <c r="L3" s="153"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="153"/>
+      <c r="O3" s="153"/>
+      <c r="P3" s="154"/>
+      <c r="Q3" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="R3" s="39" t="s">
+      <c r="R3" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="S3" s="40"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="33"/>
+      <c r="S3" s="161"/>
+      <c r="T3" s="162"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="153"/>
+      <c r="W3" s="153"/>
+      <c r="X3" s="153"/>
+      <c r="Y3" s="153"/>
+      <c r="Z3" s="153"/>
+      <c r="AA3" s="153"/>
+      <c r="AB3" s="153"/>
+      <c r="AC3" s="153"/>
+      <c r="AD3" s="153"/>
+      <c r="AE3" s="154"/>
     </row>
     <row r="4" spans="1:31" ht="9.9499999999999993" customHeight="1">
-      <c r="A4" s="50"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="47"/>
-      <c r="W4" s="47"/>
-      <c r="X4" s="47"/>
-      <c r="Y4" s="47"/>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="47"/>
-      <c r="AD4" s="47"/>
-      <c r="AE4" s="48"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="165"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="168"/>
+      <c r="G4" s="168"/>
+      <c r="H4" s="168"/>
+      <c r="I4" s="168"/>
+      <c r="J4" s="168"/>
+      <c r="K4" s="168"/>
+      <c r="L4" s="168"/>
+      <c r="M4" s="168"/>
+      <c r="N4" s="168"/>
+      <c r="O4" s="168"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="171"/>
+      <c r="R4" s="163"/>
+      <c r="S4" s="164"/>
+      <c r="T4" s="165"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
+      <c r="W4" s="168"/>
+      <c r="X4" s="168"/>
+      <c r="Y4" s="168"/>
+      <c r="Z4" s="168"/>
+      <c r="AA4" s="168"/>
+      <c r="AB4" s="168"/>
+      <c r="AC4" s="168"/>
+      <c r="AD4" s="168"/>
+      <c r="AE4" s="169"/>
     </row>
     <row r="5" spans="1:31" ht="9.9499999999999993" customHeight="1">
-      <c r="A5" s="50"/>
-      <c r="B5" s="52" t="s">
+      <c r="A5" s="171"/>
+      <c r="B5" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="52" t="s">
+      <c r="C5" s="119"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="52" t="s">
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="54"/>
-      <c r="M5" s="55" t="s">
+      <c r="L5" s="120"/>
+      <c r="M5" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="52" t="s">
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="130"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="S5" s="53"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="61"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="63"/>
-      <c r="Z5" s="52" t="s">
+      <c r="S5" s="119"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="176"/>
+      <c r="V5" s="177"/>
+      <c r="W5" s="177"/>
+      <c r="X5" s="177"/>
+      <c r="Y5" s="178"/>
+      <c r="Z5" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="52"/>
-      <c r="AC5" s="53"/>
-      <c r="AD5" s="53"/>
-      <c r="AE5" s="67"/>
+      <c r="AA5" s="120"/>
+      <c r="AB5" s="118"/>
+      <c r="AC5" s="119"/>
+      <c r="AD5" s="119"/>
+      <c r="AE5" s="182"/>
     </row>
     <row r="6" spans="1:31" ht="9.9499999999999993" customHeight="1">
-      <c r="A6" s="50"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="64"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="66"/>
-      <c r="Z6" s="42"/>
-      <c r="AA6" s="44"/>
-      <c r="AB6" s="42"/>
-      <c r="AC6" s="43"/>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="68"/>
+      <c r="A6" s="171"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="164"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="163"/>
+      <c r="F6" s="164"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="164"/>
+      <c r="I6" s="164"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="163"/>
+      <c r="L6" s="165"/>
+      <c r="M6" s="173"/>
+      <c r="N6" s="174"/>
+      <c r="O6" s="174"/>
+      <c r="P6" s="175"/>
+      <c r="Q6" s="171"/>
+      <c r="R6" s="163"/>
+      <c r="S6" s="164"/>
+      <c r="T6" s="165"/>
+      <c r="U6" s="179"/>
+      <c r="V6" s="180"/>
+      <c r="W6" s="180"/>
+      <c r="X6" s="180"/>
+      <c r="Y6" s="181"/>
+      <c r="Z6" s="163"/>
+      <c r="AA6" s="165"/>
+      <c r="AB6" s="163"/>
+      <c r="AC6" s="164"/>
+      <c r="AD6" s="164"/>
+      <c r="AE6" s="183"/>
     </row>
     <row r="7" spans="1:31" ht="12.75" customHeight="1">
-      <c r="A7" s="50"/>
-      <c r="B7" s="52" t="s">
+      <c r="A7" s="171"/>
+      <c r="B7" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="55" t="s">
+      <c r="C7" s="119"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="57"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="52" t="s">
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="171"/>
+      <c r="R7" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="53"/>
-      <c r="T7" s="54"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="56"/>
-      <c r="Z7" s="56"/>
-      <c r="AA7" s="56"/>
-      <c r="AB7" s="56"/>
-      <c r="AC7" s="56"/>
-      <c r="AD7" s="56"/>
-      <c r="AE7" s="57"/>
+      <c r="S7" s="119"/>
+      <c r="T7" s="120"/>
+      <c r="U7" s="124"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="125"/>
+      <c r="X7" s="125"/>
+      <c r="Y7" s="125"/>
+      <c r="Z7" s="125"/>
+      <c r="AA7" s="125"/>
+      <c r="AB7" s="125"/>
+      <c r="AC7" s="125"/>
+      <c r="AD7" s="125"/>
+      <c r="AE7" s="130"/>
     </row>
     <row r="8" spans="1:31" ht="12.75" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="171"/>
+      <c r="B8" s="163" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="59"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="42" t="s">
+      <c r="C8" s="164"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="174"/>
+      <c r="G8" s="174"/>
+      <c r="H8" s="174"/>
+      <c r="I8" s="174"/>
+      <c r="J8" s="174"/>
+      <c r="K8" s="174"/>
+      <c r="L8" s="174"/>
+      <c r="M8" s="174"/>
+      <c r="N8" s="174"/>
+      <c r="O8" s="174"/>
+      <c r="P8" s="175"/>
+      <c r="Q8" s="171"/>
+      <c r="R8" s="163" t="s">
         <v>13</v>
       </c>
-      <c r="S8" s="43"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="59"/>
-      <c r="W8" s="59"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="59"/>
-      <c r="Z8" s="59"/>
-      <c r="AA8" s="59"/>
-      <c r="AB8" s="59"/>
-      <c r="AC8" s="59"/>
-      <c r="AD8" s="59"/>
-      <c r="AE8" s="60"/>
+      <c r="S8" s="164"/>
+      <c r="T8" s="165"/>
+      <c r="U8" s="173"/>
+      <c r="V8" s="174"/>
+      <c r="W8" s="174"/>
+      <c r="X8" s="174"/>
+      <c r="Y8" s="174"/>
+      <c r="Z8" s="174"/>
+      <c r="AA8" s="174"/>
+      <c r="AB8" s="174"/>
+      <c r="AC8" s="174"/>
+      <c r="AD8" s="174"/>
+      <c r="AE8" s="175"/>
     </row>
     <row r="9" spans="1:31" ht="9.9499999999999993" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="52" t="s">
+      <c r="A9" s="171"/>
+      <c r="B9" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55" t="s">
+      <c r="C9" s="119"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="52" t="s">
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="54"/>
-      <c r="L9" s="55" t="s">
+      <c r="K9" s="120"/>
+      <c r="L9" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="57"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="52" t="s">
+      <c r="M9" s="125"/>
+      <c r="N9" s="125"/>
+      <c r="O9" s="125"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="171"/>
+      <c r="R9" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="S9" s="53"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="56"/>
-      <c r="X9" s="72"/>
-      <c r="Y9" s="52" t="s">
+      <c r="S9" s="119"/>
+      <c r="T9" s="120"/>
+      <c r="U9" s="124"/>
+      <c r="V9" s="125"/>
+      <c r="W9" s="125"/>
+      <c r="X9" s="126"/>
+      <c r="Y9" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="Z9" s="54"/>
-      <c r="AA9" s="55"/>
-      <c r="AB9" s="56"/>
-      <c r="AC9" s="56"/>
-      <c r="AD9" s="56"/>
-      <c r="AE9" s="57"/>
+      <c r="Z9" s="120"/>
+      <c r="AA9" s="124"/>
+      <c r="AB9" s="125"/>
+      <c r="AC9" s="125"/>
+      <c r="AD9" s="125"/>
+      <c r="AE9" s="130"/>
     </row>
-    <row r="10" spans="1:31" ht="9.9499999999999993" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="74"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="76"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="70"/>
-      <c r="T10" s="71"/>
-      <c r="U10" s="73"/>
-      <c r="V10" s="74"/>
-      <c r="W10" s="74"/>
-      <c r="X10" s="75"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="73"/>
-      <c r="AB10" s="74"/>
-      <c r="AC10" s="74"/>
-      <c r="AD10" s="74"/>
-      <c r="AE10" s="76"/>
+    <row r="10" spans="1:31" ht="9.9499999999999993" customHeight="1" thickBot="1">
+      <c r="A10" s="172"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="127"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="172"/>
+      <c r="R10" s="121"/>
+      <c r="S10" s="122"/>
+      <c r="T10" s="123"/>
+      <c r="U10" s="127"/>
+      <c r="V10" s="128"/>
+      <c r="W10" s="128"/>
+      <c r="X10" s="129"/>
+      <c r="Y10" s="121"/>
+      <c r="Z10" s="123"/>
+      <c r="AA10" s="127"/>
+      <c r="AB10" s="128"/>
+      <c r="AC10" s="128"/>
+      <c r="AD10" s="128"/>
+      <c r="AE10" s="131"/>
     </row>
     <row r="11" spans="1:31" ht="9" customHeight="1">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="132" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="84"/>
-      <c r="L11" s="84"/>
-      <c r="M11" s="84"/>
-      <c r="N11" s="84"/>
-      <c r="O11" s="84"/>
-      <c r="P11" s="87"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="95" t="s">
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="185"/>
+      <c r="H11" s="185"/>
+      <c r="I11" s="185"/>
+      <c r="J11" s="185"/>
+      <c r="K11" s="185"/>
+      <c r="L11" s="185"/>
+      <c r="M11" s="185"/>
+      <c r="N11" s="185"/>
+      <c r="O11" s="185"/>
+      <c r="P11" s="185"/>
+      <c r="Q11" s="186"/>
+      <c r="R11" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="S11" s="91"/>
-      <c r="T11" s="91"/>
-      <c r="U11" s="91"/>
-      <c r="V11" s="91"/>
-      <c r="W11" s="91"/>
-      <c r="X11" s="91"/>
-      <c r="Y11" s="91"/>
-      <c r="Z11" s="78" t="s">
+      <c r="S11" s="140"/>
+      <c r="T11" s="140"/>
+      <c r="U11" s="140"/>
+      <c r="V11" s="140"/>
+      <c r="W11" s="140"/>
+      <c r="X11" s="140"/>
+      <c r="Y11" s="140"/>
+      <c r="Z11" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="AA11" s="87"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="87"/>
-      <c r="AD11" s="87"/>
-      <c r="AE11" s="93"/>
+      <c r="AA11" s="138"/>
+      <c r="AB11" s="138"/>
+      <c r="AC11" s="138"/>
+      <c r="AD11" s="138"/>
+      <c r="AE11" s="142"/>
     </row>
-    <row r="12" spans="1:31" ht="9" customHeight="1">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="86"/>
-      <c r="N12" s="86"/>
-      <c r="O12" s="86"/>
-      <c r="P12" s="89"/>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="96"/>
-      <c r="S12" s="92"/>
-      <c r="T12" s="92"/>
-      <c r="U12" s="92"/>
-      <c r="V12" s="92"/>
-      <c r="W12" s="92"/>
-      <c r="X12" s="92"/>
-      <c r="Y12" s="92"/>
-      <c r="Z12" s="81"/>
-      <c r="AA12" s="89"/>
-      <c r="AB12" s="89"/>
-      <c r="AC12" s="89"/>
-      <c r="AD12" s="89"/>
-      <c r="AE12" s="94"/>
+    <row r="12" spans="1:31" ht="9" customHeight="1" thickBot="1">
+      <c r="A12" s="135"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="188"/>
+      <c r="H12" s="188"/>
+      <c r="I12" s="188"/>
+      <c r="J12" s="188"/>
+      <c r="K12" s="188"/>
+      <c r="L12" s="188"/>
+      <c r="M12" s="188"/>
+      <c r="N12" s="188"/>
+      <c r="O12" s="188"/>
+      <c r="P12" s="188"/>
+      <c r="Q12" s="189"/>
+      <c r="R12" s="145"/>
+      <c r="S12" s="141"/>
+      <c r="T12" s="141"/>
+      <c r="U12" s="141"/>
+      <c r="V12" s="141"/>
+      <c r="W12" s="141"/>
+      <c r="X12" s="141"/>
+      <c r="Y12" s="141"/>
+      <c r="Z12" s="136"/>
+      <c r="AA12" s="139"/>
+      <c r="AB12" s="139"/>
+      <c r="AC12" s="139"/>
+      <c r="AD12" s="139"/>
+      <c r="AE12" s="143"/>
     </row>
     <row r="13" spans="1:31" ht="17.45" customHeight="1">
       <c r="A13" s="2" t="s">
@@ -2522,391 +2522,391 @@
       <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C13" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="97" t="s">
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="O13" s="98"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="97" t="s">
+      <c r="O13" s="102"/>
+      <c r="P13" s="103"/>
+      <c r="Q13" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="R13" s="98"/>
-      <c r="S13" s="99"/>
-      <c r="T13" s="97" t="s">
+      <c r="R13" s="102"/>
+      <c r="S13" s="103"/>
+      <c r="T13" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="U13" s="98"/>
-      <c r="V13" s="98"/>
-      <c r="W13" s="99"/>
-      <c r="X13" s="97" t="s">
+      <c r="U13" s="102"/>
+      <c r="V13" s="102"/>
+      <c r="W13" s="103"/>
+      <c r="X13" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="Y13" s="98"/>
-      <c r="Z13" s="98"/>
-      <c r="AA13" s="98"/>
-      <c r="AB13" s="100"/>
-      <c r="AC13" s="101" t="s">
+      <c r="Y13" s="102"/>
+      <c r="Z13" s="102"/>
+      <c r="AA13" s="102"/>
+      <c r="AB13" s="104"/>
+      <c r="AC13" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="AD13" s="102"/>
-      <c r="AE13" s="103"/>
+      <c r="AD13" s="106"/>
+      <c r="AE13" s="107"/>
     </row>
     <row r="14" spans="1:31" ht="17.45" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="104"/>
-      <c r="O14" s="105"/>
-      <c r="P14" s="106"/>
-      <c r="Q14" s="107"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="109"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111"/>
-      <c r="W14" s="112"/>
-      <c r="X14" s="110"/>
-      <c r="Y14" s="111"/>
-      <c r="Z14" s="111"/>
-      <c r="AA14" s="111"/>
-      <c r="AB14" s="112"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="111"/>
-      <c r="AE14" s="113"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="109"/>
+      <c r="K14" s="109"/>
+      <c r="L14" s="109"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="109"/>
+      <c r="P14" s="110"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="112"/>
+      <c r="S14" s="113"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="115"/>
+      <c r="V14" s="115"/>
+      <c r="W14" s="116"/>
+      <c r="X14" s="114"/>
+      <c r="Y14" s="115"/>
+      <c r="Z14" s="115"/>
+      <c r="AA14" s="115"/>
+      <c r="AB14" s="116"/>
+      <c r="AC14" s="114"/>
+      <c r="AD14" s="115"/>
+      <c r="AE14" s="117"/>
     </row>
     <row r="15" spans="1:31" ht="17.45" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="115"/>
-      <c r="L15" s="115"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="115"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="117"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="119"/>
-      <c r="T15" s="120"/>
-      <c r="U15" s="121"/>
-      <c r="V15" s="121"/>
-      <c r="W15" s="122"/>
-      <c r="X15" s="120"/>
-      <c r="Y15" s="121"/>
-      <c r="Z15" s="121"/>
-      <c r="AA15" s="121"/>
-      <c r="AB15" s="122"/>
-      <c r="AC15" s="120"/>
-      <c r="AD15" s="121"/>
-      <c r="AE15" s="123"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="82"/>
+      <c r="L15" s="82"/>
+      <c r="M15" s="83"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="85"/>
+      <c r="S15" s="86"/>
+      <c r="T15" s="87"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="89"/>
+      <c r="X15" s="87"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="89"/>
+      <c r="AC15" s="87"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="90"/>
     </row>
     <row r="16" spans="1:31" ht="17.45" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="115"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="117"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="119"/>
-      <c r="T16" s="120"/>
-      <c r="U16" s="121"/>
-      <c r="V16" s="121"/>
-      <c r="W16" s="122"/>
-      <c r="X16" s="120"/>
-      <c r="Y16" s="121"/>
-      <c r="Z16" s="121"/>
-      <c r="AA16" s="121"/>
-      <c r="AB16" s="122"/>
-      <c r="AC16" s="120"/>
-      <c r="AD16" s="121"/>
-      <c r="AE16" s="123"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="82"/>
+      <c r="M16" s="83"/>
+      <c r="N16" s="81"/>
+      <c r="O16" s="82"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="86"/>
+      <c r="T16" s="87"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="89"/>
+      <c r="X16" s="87"/>
+      <c r="Y16" s="88"/>
+      <c r="Z16" s="88"/>
+      <c r="AA16" s="88"/>
+      <c r="AB16" s="89"/>
+      <c r="AC16" s="87"/>
+      <c r="AD16" s="88"/>
+      <c r="AE16" s="90"/>
     </row>
     <row r="17" spans="1:53" ht="17.45" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="115"/>
-      <c r="M17" s="116"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="115"/>
-      <c r="P17" s="116"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="118"/>
-      <c r="S17" s="119"/>
-      <c r="T17" s="120"/>
-      <c r="U17" s="121"/>
-      <c r="V17" s="121"/>
-      <c r="W17" s="122"/>
-      <c r="X17" s="120"/>
-      <c r="Y17" s="121"/>
-      <c r="Z17" s="121"/>
-      <c r="AA17" s="121"/>
-      <c r="AB17" s="122"/>
-      <c r="AC17" s="120"/>
-      <c r="AD17" s="121"/>
-      <c r="AE17" s="123"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
+      <c r="L17" s="82"/>
+      <c r="M17" s="83"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="82"/>
+      <c r="P17" s="83"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="85"/>
+      <c r="S17" s="86"/>
+      <c r="T17" s="87"/>
+      <c r="U17" s="88"/>
+      <c r="V17" s="88"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="87"/>
+      <c r="Y17" s="88"/>
+      <c r="Z17" s="88"/>
+      <c r="AA17" s="88"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="88"/>
+      <c r="AE17" s="90"/>
     </row>
     <row r="18" spans="1:53" ht="17.45" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="114"/>
-      <c r="O18" s="115"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="117"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="120"/>
-      <c r="U18" s="121"/>
-      <c r="V18" s="121"/>
-      <c r="W18" s="122"/>
-      <c r="X18" s="120"/>
-      <c r="Y18" s="121"/>
-      <c r="Z18" s="121"/>
-      <c r="AA18" s="121"/>
-      <c r="AB18" s="122"/>
-      <c r="AC18" s="120"/>
-      <c r="AD18" s="121"/>
-      <c r="AE18" s="123"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="82"/>
+      <c r="M18" s="83"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="82"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="86"/>
+      <c r="T18" s="87"/>
+      <c r="U18" s="88"/>
+      <c r="V18" s="88"/>
+      <c r="W18" s="89"/>
+      <c r="X18" s="87"/>
+      <c r="Y18" s="88"/>
+      <c r="Z18" s="88"/>
+      <c r="AA18" s="88"/>
+      <c r="AB18" s="89"/>
+      <c r="AC18" s="87"/>
+      <c r="AD18" s="88"/>
+      <c r="AE18" s="90"/>
     </row>
     <row r="19" spans="1:53" ht="17.45" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="115"/>
-      <c r="M19" s="116"/>
-      <c r="N19" s="114"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="116"/>
-      <c r="Q19" s="117"/>
-      <c r="R19" s="118"/>
-      <c r="S19" s="119"/>
-      <c r="T19" s="120"/>
-      <c r="U19" s="121"/>
-      <c r="V19" s="121"/>
-      <c r="W19" s="122"/>
-      <c r="X19" s="120"/>
-      <c r="Y19" s="121"/>
-      <c r="Z19" s="121"/>
-      <c r="AA19" s="121"/>
-      <c r="AB19" s="122"/>
-      <c r="AC19" s="120"/>
-      <c r="AD19" s="121"/>
-      <c r="AE19" s="123"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="82"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="82"/>
+      <c r="L19" s="82"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="81"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="85"/>
+      <c r="S19" s="86"/>
+      <c r="T19" s="87"/>
+      <c r="U19" s="88"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="89"/>
+      <c r="X19" s="87"/>
+      <c r="Y19" s="88"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="88"/>
+      <c r="AB19" s="89"/>
+      <c r="AC19" s="87"/>
+      <c r="AD19" s="88"/>
+      <c r="AE19" s="90"/>
     </row>
     <row r="20" spans="1:53" ht="17.45" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="125"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="125"/>
-      <c r="K20" s="125"/>
-      <c r="L20" s="125"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="124"/>
-      <c r="O20" s="125"/>
-      <c r="P20" s="126"/>
-      <c r="Q20" s="127"/>
-      <c r="R20" s="128"/>
-      <c r="S20" s="129"/>
-      <c r="T20" s="130"/>
-      <c r="U20" s="131"/>
-      <c r="V20" s="131"/>
-      <c r="W20" s="132"/>
-      <c r="X20" s="130"/>
-      <c r="Y20" s="131"/>
-      <c r="Z20" s="131"/>
-      <c r="AA20" s="131"/>
-      <c r="AB20" s="132"/>
-      <c r="AC20" s="130"/>
-      <c r="AD20" s="131"/>
-      <c r="AE20" s="133"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="92"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="92"/>
+      <c r="M20" s="93"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="92"/>
+      <c r="P20" s="93"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="95"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="97"/>
+      <c r="U20" s="98"/>
+      <c r="V20" s="98"/>
+      <c r="W20" s="99"/>
+      <c r="X20" s="97"/>
+      <c r="Y20" s="98"/>
+      <c r="Z20" s="98"/>
+      <c r="AA20" s="98"/>
+      <c r="AB20" s="99"/>
+      <c r="AC20" s="97"/>
+      <c r="AD20" s="98"/>
+      <c r="AE20" s="100"/>
       <c r="BA20" s="12"/>
     </row>
     <row r="21" spans="1:53" ht="16.5" customHeight="1">
-      <c r="A21" s="134" t="s">
+      <c r="A21" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="135"/>
-      <c r="C21" s="138">
+      <c r="B21" s="47"/>
+      <c r="C21" s="49">
         <f>SUM(Q14:S20)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="139"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="144" t="s">
+      <c r="D21" s="50"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="145"/>
-      <c r="H21" s="146"/>
-      <c r="I21" s="147"/>
-      <c r="J21" s="147"/>
-      <c r="K21" s="148"/>
-      <c r="L21" s="152" t="s">
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="M21" s="153"/>
-      <c r="N21" s="156"/>
-      <c r="O21" s="157"/>
-      <c r="P21" s="158"/>
-      <c r="Q21" s="152" t="s">
+      <c r="M21" s="64"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="R21" s="162"/>
-      <c r="S21" s="135"/>
-      <c r="T21" s="163"/>
-      <c r="U21" s="164"/>
-      <c r="V21" s="164"/>
-      <c r="W21" s="164"/>
-      <c r="X21" s="164"/>
-      <c r="Y21" s="165"/>
-      <c r="Z21" s="169" t="s">
+      <c r="R21" s="72"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="73"/>
+      <c r="U21" s="74"/>
+      <c r="V21" s="74"/>
+      <c r="W21" s="74"/>
+      <c r="X21" s="74"/>
+      <c r="Y21" s="75"/>
+      <c r="Z21" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="AA21" s="170"/>
-      <c r="AB21" s="171"/>
-      <c r="AC21" s="169"/>
-      <c r="AD21" s="170"/>
-      <c r="AE21" s="175"/>
+      <c r="AA21" s="26"/>
+      <c r="AB21" s="79"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="26"/>
+      <c r="AE21" s="27"/>
     </row>
     <row r="22" spans="1:53" ht="15" customHeight="1">
-      <c r="A22" s="136"/>
-      <c r="B22" s="137"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="142"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="154" t="s">
+      <c r="A22" s="48"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="137"/>
-      <c r="H22" s="149"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="150"/>
-      <c r="K22" s="151"/>
-      <c r="L22" s="154"/>
-      <c r="M22" s="155"/>
-      <c r="N22" s="159"/>
-      <c r="O22" s="160"/>
-      <c r="P22" s="161"/>
-      <c r="Q22" s="154" t="s">
+      <c r="G22" s="32"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="R22" s="177"/>
-      <c r="S22" s="137"/>
-      <c r="T22" s="166"/>
-      <c r="U22" s="167"/>
-      <c r="V22" s="167"/>
-      <c r="W22" s="167"/>
-      <c r="X22" s="167"/>
-      <c r="Y22" s="168"/>
-      <c r="Z22" s="172"/>
-      <c r="AA22" s="173"/>
-      <c r="AB22" s="174"/>
-      <c r="AC22" s="172"/>
-      <c r="AD22" s="173"/>
-      <c r="AE22" s="176"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="76"/>
+      <c r="U22" s="77"/>
+      <c r="V22" s="77"/>
+      <c r="W22" s="77"/>
+      <c r="X22" s="77"/>
+      <c r="Y22" s="78"/>
+      <c r="Z22" s="28"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="80"/>
+      <c r="AC22" s="28"/>
+      <c r="AD22" s="29"/>
+      <c r="AE22" s="30"/>
     </row>
     <row r="23" spans="1:53" ht="17.25" customHeight="1">
-      <c r="A23" s="178" t="s">
+      <c r="A23" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="179"/>
-      <c r="C23" s="179"/>
-      <c r="D23" s="179"/>
-      <c r="E23" s="179"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="179"/>
-      <c r="H23" s="179"/>
-      <c r="I23" s="179"/>
-      <c r="J23" s="179"/>
-      <c r="K23" s="179"/>
-      <c r="L23" s="179"/>
-      <c r="M23" s="179"/>
-      <c r="N23" s="179"/>
-      <c r="O23" s="179"/>
-      <c r="P23" s="179"/>
-      <c r="Q23" s="179"/>
-      <c r="R23" s="179"/>
-      <c r="S23" s="179"/>
-      <c r="T23" s="179"/>
-      <c r="U23" s="179"/>
-      <c r="V23" s="179"/>
-      <c r="W23" s="179"/>
-      <c r="X23" s="179"/>
-      <c r="Y23" s="180"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="36"/>
       <c r="Z23" s="13"/>
       <c r="AA23" s="13"/>
       <c r="AB23" s="13"/>
@@ -2916,33 +2916,33 @@
       <c r="AG23" s="15"/>
     </row>
     <row r="24" spans="1:53" ht="15" customHeight="1">
-      <c r="A24" s="181" t="s">
+      <c r="A24" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="182"/>
-      <c r="C24" s="182"/>
-      <c r="D24" s="182"/>
-      <c r="E24" s="182"/>
-      <c r="F24" s="182"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="182"/>
-      <c r="I24" s="182"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="182"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="182"/>
-      <c r="N24" s="182"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="182"/>
-      <c r="Q24" s="182"/>
-      <c r="R24" s="182"/>
-      <c r="S24" s="182"/>
-      <c r="T24" s="182"/>
-      <c r="U24" s="182"/>
-      <c r="V24" s="182"/>
-      <c r="W24" s="182"/>
-      <c r="X24" s="182"/>
-      <c r="Y24" s="183"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="38"/>
+      <c r="V24" s="38"/>
+      <c r="W24" s="38"/>
+      <c r="X24" s="38"/>
+      <c r="Y24" s="39"/>
       <c r="Z24" s="16"/>
       <c r="AA24" s="16"/>
       <c r="AB24" s="16"/>
@@ -2953,39 +2953,39 @@
       <c r="AG24" s="15"/>
     </row>
     <row r="25" spans="1:53" ht="15" customHeight="1">
-      <c r="A25" s="184"/>
-      <c r="B25" s="185"/>
-      <c r="C25" s="185"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="185"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="185"/>
-      <c r="H25" s="185"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="185"/>
-      <c r="M25" s="185"/>
-      <c r="N25" s="185"/>
-      <c r="O25" s="185"/>
-      <c r="P25" s="185"/>
-      <c r="Q25" s="185"/>
-      <c r="R25" s="185"/>
-      <c r="S25" s="185"/>
-      <c r="T25" s="185"/>
-      <c r="U25" s="185"/>
-      <c r="V25" s="185"/>
-      <c r="W25" s="185"/>
-      <c r="X25" s="185"/>
-      <c r="Y25" s="186"/>
-      <c r="Z25" s="187" t="s">
+      <c r="A25" s="40"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="41"/>
+      <c r="X25" s="41"/>
+      <c r="Y25" s="42"/>
+      <c r="Z25" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AA25" s="188"/>
-      <c r="AB25" s="188"/>
-      <c r="AC25" s="188"/>
-      <c r="AD25" s="188"/>
-      <c r="AE25" s="189"/>
+      <c r="AA25" s="44"/>
+      <c r="AB25" s="44"/>
+      <c r="AC25" s="44"/>
+      <c r="AD25" s="44"/>
+      <c r="AE25" s="45"/>
       <c r="AF25" s="19"/>
       <c r="AG25" s="20"/>
     </row>
@@ -3025,85 +3025,7 @@
       <c r="AG26" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="102">
-    <mergeCell ref="AC21:AE22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="A23:Y23"/>
-    <mergeCell ref="A24:Y25"/>
-    <mergeCell ref="Z25:AE25"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:E22"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:K22"/>
-    <mergeCell ref="L21:M22"/>
-    <mergeCell ref="N21:P22"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="T21:Y22"/>
-    <mergeCell ref="Z21:AB22"/>
-    <mergeCell ref="C19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="X19:AB19"/>
-    <mergeCell ref="AC19:AE19"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="X20:AB20"/>
-    <mergeCell ref="AC20:AE20"/>
-    <mergeCell ref="C17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:AB17"/>
-    <mergeCell ref="AC17:AE17"/>
-    <mergeCell ref="C18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="X18:AB18"/>
-    <mergeCell ref="AC18:AE18"/>
-    <mergeCell ref="C15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="X15:AB15"/>
-    <mergeCell ref="AC15:AE15"/>
-    <mergeCell ref="C16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="X16:AB16"/>
-    <mergeCell ref="AC16:AE16"/>
-    <mergeCell ref="C13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="T13:W13"/>
-    <mergeCell ref="X13:AB13"/>
-    <mergeCell ref="AC13:AE13"/>
-    <mergeCell ref="C14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="X14:AB14"/>
-    <mergeCell ref="AC14:AE14"/>
-    <mergeCell ref="B9:D10"/>
-    <mergeCell ref="E9:I10"/>
-    <mergeCell ref="J9:K10"/>
-    <mergeCell ref="L9:P10"/>
-    <mergeCell ref="R9:T10"/>
-    <mergeCell ref="U9:X10"/>
-    <mergeCell ref="Y9:Z10"/>
-    <mergeCell ref="AA9:AE10"/>
-    <mergeCell ref="A11:E12"/>
-    <mergeCell ref="F11:O12"/>
-    <mergeCell ref="P11:Q12"/>
-    <mergeCell ref="S11:Y12"/>
-    <mergeCell ref="AA11:AE12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="Z11:Z12"/>
+  <mergeCells count="101">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:Y2"/>
     <mergeCell ref="Z1:AE2"/>
@@ -3128,6 +3050,83 @@
     <mergeCell ref="U7:AE8"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="B9:D10"/>
+    <mergeCell ref="E9:I10"/>
+    <mergeCell ref="J9:K10"/>
+    <mergeCell ref="L9:P10"/>
+    <mergeCell ref="R9:T10"/>
+    <mergeCell ref="U9:X10"/>
+    <mergeCell ref="Y9:Z10"/>
+    <mergeCell ref="AA9:AE10"/>
+    <mergeCell ref="A11:E12"/>
+    <mergeCell ref="S11:Y12"/>
+    <mergeCell ref="AA11:AE12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="F11:Q12"/>
+    <mergeCell ref="C13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="X13:AB13"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="C14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="X14:AB14"/>
+    <mergeCell ref="AC14:AE14"/>
+    <mergeCell ref="C15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="X15:AB15"/>
+    <mergeCell ref="AC15:AE15"/>
+    <mergeCell ref="C16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="X16:AB16"/>
+    <mergeCell ref="AC16:AE16"/>
+    <mergeCell ref="C17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:AB17"/>
+    <mergeCell ref="AC17:AE17"/>
+    <mergeCell ref="C18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="X18:AB18"/>
+    <mergeCell ref="AC18:AE18"/>
+    <mergeCell ref="C19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="X19:AB19"/>
+    <mergeCell ref="AC19:AE19"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="X20:AB20"/>
+    <mergeCell ref="AC20:AE20"/>
+    <mergeCell ref="AC21:AE22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="A23:Y23"/>
+    <mergeCell ref="A24:Y25"/>
+    <mergeCell ref="Z25:AE25"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:E22"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:K22"/>
+    <mergeCell ref="L21:M22"/>
+    <mergeCell ref="N21:P22"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="T21:Y22"/>
+    <mergeCell ref="Z21:AB22"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
